--- a/PERSONAL KAROLAY/FINANZAS/Presupuesto.xlsx
+++ b/PERSONAL KAROLAY/FINANZAS/Presupuesto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documentos\PERSONAL KAROLAY\FINANZAS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documentos\Personal_Karoaly\PERSONAL KAROLAY\FINANZAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC174BE-F7BC-40BD-980A-CF1E3C31F095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7C7107-75B3-4AC6-A53D-FB0AF1085F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{7556E4C5-DE0A-4637-88DF-B694AE5EFB5B}"/>
   </bookViews>
@@ -631,7 +631,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="5">
-        <v>550000</v>
+        <v>640000</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>10</v>
@@ -655,7 +655,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="5">
-        <v>1157000</v>
+        <v>1157200</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>22</v>
@@ -685,7 +685,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="26">
-        <v>105000</v>
+        <v>106000</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -733,7 +733,7 @@
         <v>19</v>
       </c>
       <c r="E9" s="26">
-        <v>396000</v>
+        <v>488000</v>
       </c>
       <c r="F9" s="2"/>
       <c r="H9" s="14"/>
@@ -751,7 +751,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="26">
-        <v>97000</v>
+        <v>106000</v>
       </c>
       <c r="F10" s="2"/>
       <c r="H10" s="14"/>
@@ -821,14 +821,14 @@
       <c r="B14" s="6"/>
       <c r="C14" s="7">
         <f>SUM(C5:C13)</f>
-        <v>2354000</v>
+        <v>2444200</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E14" s="7">
         <f>SUM(E5:E11)</f>
-        <v>1471000</v>
+        <v>1573000</v>
       </c>
       <c r="F14" s="2"/>
       <c r="H14" s="13"/>
